--- a/outputs/daily/hr_rankings_2026-10-27.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-27.xlsx
@@ -845,7 +845,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>58.6</v>
+        <v>58.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>55.6</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -910,12 +910,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1163,14 +1163,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>56.5</v>
+        <v>56.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>55.6</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>60</v>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1775,24 +1775,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -1805,26 +1805,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>52</v>
+        <v>54.5</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1838,26 +1826,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>36.6</v>
+        <v>48.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R5" t="n">
         <v>55.6</v>
       </c>
       <c r="S5" t="n">
-        <v>81.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T5" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U5" t="n">
-        <v>65.2</v>
+        <v>28.9</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -1870,24 +1858,24 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -1900,7 +1888,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr"/>
@@ -1917,27 +1905,27 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1947,99 +1935,75 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.1715</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr">
         <is>
           <t>40 deg</t>
@@ -2093,12 +2057,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2123,7 +2087,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2142,7 +2106,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>51.9</v>
+        <v>53.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2160,7 +2124,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>38.2</v>
+        <v>36.6</v>
       </c>
       <c r="Q6" t="n">
         <v>40.1</v>
@@ -2169,13 +2133,13 @@
         <v>55.6</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>25.3</v>
+        <v>65.2</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -2188,12 +2152,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2235,22 +2199,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -2265,67 +2229,67 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -2411,24 +2375,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -2441,14 +2405,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>51.4</v>
+        <v>52.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2462,26 +2438,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>43.3</v>
+        <v>47.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R7" t="n">
         <v>55.6</v>
       </c>
       <c r="S7" t="n">
-        <v>95.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -2494,24 +2470,24 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -2524,7 +2500,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr"/>
@@ -2541,12 +2517,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2556,72 +2532,72 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -2631,15 +2607,39 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1288</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>0.1342</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>40 deg</t>
@@ -2693,24 +2693,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Victor Mesa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -2726,23 +2726,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>51.2</v>
+        <v>50.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2756,14 +2744,14 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>47.1</v>
+        <v>43.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R8" t="n">
         <v>55.6</v>
@@ -2772,10 +2760,10 @@
         <v>71.7</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U8" t="n">
-        <v>13.3</v>
+        <v>54.9</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -2788,24 +2776,24 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -2818,7 +2806,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr"/>
@@ -2835,129 +2823,105 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>32.39</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1342</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
+          <t>0.2134</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr">
         <is>
           <t>40 deg</t>
@@ -3094,7 +3058,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -3388,7 +3352,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -3611,24 +3575,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -3641,14 +3605,26 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L11" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3662,26 +3638,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>43.6</v>
+        <v>38.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R11" t="n">
         <v>55.6</v>
       </c>
       <c r="S11" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T11" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>54.9</v>
+        <v>25.3</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -3694,24 +3670,24 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -3724,7 +3700,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr"/>
@@ -3741,12 +3717,12 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -3756,12 +3732,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -3771,75 +3747,99 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>32.46</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.2134</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+          <t>0.1565</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>40 deg</t>
@@ -3893,12 +3893,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3923,14 +3923,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>41.4</v>
+        <v>40.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3944,11 +3944,11 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
         <v>41.2</v>
@@ -3957,13 +3957,13 @@
         <v>55.6</v>
       </c>
       <c r="S12" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T12" t="n">
         <v>60</v>
       </c>
       <c r="U12" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -3976,12 +3976,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -4023,22 +4023,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -4053,67 +4053,67 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr"/>
@@ -4175,12 +4175,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>810938</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ben Williamson</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4205,14 +4205,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>39.6</v>
+        <v>39.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4226,11 +4226,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>11.6</v>
+        <v>10.6</v>
       </c>
       <c r="Q13" t="n">
         <v>41.2</v>
@@ -4239,13 +4239,13 @@
         <v>55.6</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T13" t="n">
         <v>60</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4258,12 +4258,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -4305,22 +4305,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
@@ -4335,67 +4335,67 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>35.39</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>98.4446</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3241</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.0789</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2809</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.0731</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr"/>
@@ -4457,24 +4457,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -4487,14 +4487,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L14" t="n">
-        <v>38.3</v>
+        <v>37.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4508,26 +4520,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.2</v>
+        <v>16.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>38.7</v>
       </c>
       <c r="R14" t="n">
         <v>55.6</v>
       </c>
       <c r="S14" t="n">
-        <v>92.09999999999999</v>
+        <v>47.9</v>
       </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U14" t="n">
-        <v>15.3</v>
+        <v>5.1</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -4540,24 +4552,24 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -4570,7 +4582,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr"/>
@@ -4587,12 +4599,12 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -4602,12 +4614,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -4617,75 +4629,99 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>98.8409</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+          <t>0.079</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>40 deg</t>
@@ -4739,24 +4775,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -4769,26 +4805,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>36.4</v>
+        <v>37</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4806,22 +4830,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>10.5</v>
+        <v>15.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R15" t="n">
         <v>55.6</v>
       </c>
       <c r="S15" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U15" t="n">
-        <v>24.9</v>
+        <v>19.5</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -4834,24 +4858,24 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -4864,7 +4888,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr"/>
@@ -4881,12 +4905,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -4896,12 +4920,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -4911,99 +4935,75 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.087</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
+          <t>0.133</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
         <is>
           <t>40 deg</t>
@@ -5057,24 +5057,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -5087,26 +5087,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>36.2</v>
+        <v>36.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5120,26 +5108,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>11.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R16" t="n">
         <v>55.6</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U16" t="n">
-        <v>23.7</v>
+        <v>15.3</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5152,24 +5140,24 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -5182,7 +5170,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
@@ -5199,12 +5187,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -5214,12 +5202,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -5229,99 +5217,75 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1042</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr">
         <is>
           <t>40 deg</t>
@@ -5375,24 +5339,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -5405,14 +5369,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L17" t="n">
-        <v>36.2</v>
+        <v>36.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5430,22 +5406,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>12.8</v>
+        <v>10.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R17" t="n">
         <v>55.6</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>18.3</v>
+        <v>24.9</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5458,24 +5434,24 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -5488,7 +5464,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -5505,27 +5481,27 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -5535,75 +5511,99 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.1186</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+          <t>0.087</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>40 deg</t>
@@ -5657,12 +5657,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5706,7 +5706,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>35.1</v>
+        <v>36.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>5.4</v>
+        <v>11.1</v>
       </c>
       <c r="Q18" t="n">
         <v>40.1</v>
@@ -5733,13 +5733,13 @@
         <v>55.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T18" t="n">
         <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>17.3</v>
+        <v>23.7</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
@@ -5829,67 +5829,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.0974</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6712,7 +6712,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>58.6</v>
+        <v>58.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>55.6</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -7011,14 +7011,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>56.5</v>
+        <v>56.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>55.6</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>60</v>
@@ -7066,12 +7066,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -7623,24 +7623,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -7653,26 +7653,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>52</v>
+        <v>54.5</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7686,26 +7674,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>36.6</v>
+        <v>48.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R5" t="n">
         <v>55.6</v>
       </c>
       <c r="S5" t="n">
-        <v>81.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T5" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U5" t="n">
-        <v>65.2</v>
+        <v>28.9</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -7718,24 +7706,24 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -7748,7 +7736,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr"/>
@@ -7765,27 +7753,27 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -7795,99 +7783,75 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.1715</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr">
         <is>
           <t>40 deg</t>
@@ -7941,12 +7905,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7971,7 +7935,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -7990,7 +7954,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>51.9</v>
+        <v>53.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8008,7 +7972,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>38.2</v>
+        <v>36.6</v>
       </c>
       <c r="Q6" t="n">
         <v>40.1</v>
@@ -8017,13 +7981,13 @@
         <v>55.6</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>25.3</v>
+        <v>65.2</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -8036,12 +8000,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -8083,22 +8047,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -8113,67 +8077,67 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -8259,24 +8223,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -8289,14 +8253,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>51.4</v>
+        <v>52.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8310,26 +8286,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>43.3</v>
+        <v>47.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R7" t="n">
         <v>55.6</v>
       </c>
       <c r="S7" t="n">
-        <v>95.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -8342,24 +8318,24 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -8372,7 +8348,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr"/>
@@ -8389,12 +8365,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -8404,72 +8380,72 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -8479,15 +8455,39 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1288</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>0.1342</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>40 deg</t>
@@ -8541,24 +8541,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Victor Mesa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -8574,23 +8574,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>51.2</v>
+        <v>50.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8604,14 +8592,14 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>47.1</v>
+        <v>43.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R8" t="n">
         <v>55.6</v>
@@ -8620,10 +8608,10 @@
         <v>71.7</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U8" t="n">
-        <v>13.3</v>
+        <v>54.9</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -8636,24 +8624,24 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -8666,7 +8654,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr"/>
@@ -8683,129 +8671,105 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>32.39</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1342</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
+          <t>0.2134</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr">
         <is>
           <t>40 deg</t>
@@ -8942,7 +8906,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -9236,7 +9200,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -9459,24 +9423,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -9489,14 +9453,26 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L11" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9510,26 +9486,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>43.6</v>
+        <v>38.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R11" t="n">
         <v>55.6</v>
       </c>
       <c r="S11" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T11" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>54.9</v>
+        <v>25.3</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -9542,24 +9518,24 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -9572,7 +9548,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr"/>
@@ -9589,12 +9565,12 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -9604,12 +9580,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -9619,75 +9595,99 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>32.46</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.2134</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+          <t>0.1565</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>40 deg</t>
@@ -9741,12 +9741,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -9771,14 +9771,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>41.4</v>
+        <v>40.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9792,11 +9792,11 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
         <v>41.2</v>
@@ -9805,13 +9805,13 @@
         <v>55.6</v>
       </c>
       <c r="S12" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T12" t="n">
         <v>60</v>
       </c>
       <c r="U12" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -9824,12 +9824,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -9871,22 +9871,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -9901,67 +9901,67 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr"/>
@@ -10023,12 +10023,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>810938</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ben Williamson</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -10053,14 +10053,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>39.6</v>
+        <v>39.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10074,11 +10074,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>11.6</v>
+        <v>10.6</v>
       </c>
       <c r="Q13" t="n">
         <v>41.2</v>
@@ -10087,13 +10087,13 @@
         <v>55.6</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T13" t="n">
         <v>60</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -10106,12 +10106,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -10153,22 +10153,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
@@ -10183,67 +10183,67 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>35.39</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>98.4446</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3241</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.0789</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2809</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.0731</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr"/>
@@ -10305,24 +10305,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -10335,14 +10335,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L14" t="n">
-        <v>38.3</v>
+        <v>37.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10356,26 +10368,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.2</v>
+        <v>16.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>38.7</v>
       </c>
       <c r="R14" t="n">
         <v>55.6</v>
       </c>
       <c r="S14" t="n">
-        <v>92.09999999999999</v>
+        <v>47.9</v>
       </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U14" t="n">
-        <v>15.3</v>
+        <v>5.1</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -10388,24 +10400,24 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -10418,7 +10430,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr"/>
@@ -10435,12 +10447,12 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -10450,12 +10462,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -10465,75 +10477,99 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>98.8409</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+          <t>0.079</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>40 deg</t>
@@ -10587,24 +10623,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -10617,26 +10653,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>36.4</v>
+        <v>37</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -10654,22 +10678,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>10.5</v>
+        <v>15.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R15" t="n">
         <v>55.6</v>
       </c>
       <c r="S15" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U15" t="n">
-        <v>24.9</v>
+        <v>19.5</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -10682,24 +10706,24 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -10712,7 +10736,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr"/>
@@ -10729,12 +10753,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -10744,12 +10768,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -10759,99 +10783,75 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.087</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
+          <t>0.133</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
         <is>
           <t>40 deg</t>
@@ -10905,24 +10905,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -10935,26 +10935,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Griffin Jax</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>643377</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>36.2</v>
+        <v>36.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10968,26 +10956,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>11.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R16" t="n">
         <v>55.6</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U16" t="n">
-        <v>23.7</v>
+        <v>15.3</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -11000,24 +10988,24 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -11030,7 +11018,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
@@ -11047,12 +11035,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -11062,12 +11050,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -11077,99 +11065,75 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1042</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>40.67</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>88.78</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>0.3923</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>0.1478</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr">
         <is>
           <t>40 deg</t>
@@ -11223,24 +11187,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -11253,14 +11217,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L17" t="n">
-        <v>36.2</v>
+        <v>36.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11278,22 +11254,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>12.8</v>
+        <v>10.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R17" t="n">
         <v>55.6</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>18.3</v>
+        <v>24.9</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -11306,24 +11282,24 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -11336,7 +11312,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -11353,27 +11329,27 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -11383,75 +11359,99 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.1186</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+          <t>0.087</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>40 deg</t>
@@ -11505,12 +11505,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -11554,7 +11554,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>35.1</v>
+        <v>36.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>5.4</v>
+        <v>11.1</v>
       </c>
       <c r="Q18" t="n">
         <v>40.1</v>
@@ -11581,13 +11581,13 @@
         <v>55.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T18" t="n">
         <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>17.3</v>
+        <v>23.7</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -11600,12 +11600,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -11647,12 +11647,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -11662,7 +11662,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
@@ -11677,67 +11677,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.0974</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-10-27.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-27.xlsx
@@ -840,12 +840,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>58.1</v>
+        <v>59.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -891,7 +891,7 @@
         <v>55.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -905,39 +905,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1082,7 +1078,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1133,12 +1129,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1148,7 +1144,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1158,19 +1154,31 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Dustin May</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>669160</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>56.8</v>
+        <v>57.9</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1184,71 +1192,65 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>61.9</v>
+        <v>48.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.2</v>
+        <v>46.2</v>
       </c>
       <c r="R3" t="n">
         <v>55.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U3" t="n">
-        <v>37.8</v>
+        <v>28.9</v>
       </c>
       <c r="V3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W3" t="n">
-        <v>48</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr"/>
@@ -1265,130 +1267,154 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Last 7 games: 4/21, 1 HR</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>10.8</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>48.55</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>91.67</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>101.2282</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.4611</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.196</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.3547</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>70.36</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>13.11</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>33.13</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>30.13</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>44.36</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>90.18</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.4132</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.1595</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>13.37</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>50.21</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>92.61</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>104.9857</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.4996</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.232</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.3586</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>79.13</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>83.64</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>44.89</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>23.28</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>0.2549</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>40 deg</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="BN3" t="inlineStr">
         <is>
           <t>75</t>
@@ -1400,56 +1426,16 @@
         </is>
       </c>
       <c r="BP3" t="inlineStr"/>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>Ballpark Pal top hitter 27.9%; best park/weather on slate</t>
-        </is>
-      </c>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="inlineStr"/>
+      <c r="BX3" t="inlineStr"/>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1457,22 +1443,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1482,22 +1468,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1506,7 +1492,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>54.6</v>
+        <v>57.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1520,66 +1506,64 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>50.1</v>
+        <v>61.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>40.1</v>
+        <v>46.2</v>
       </c>
       <c r="R4" t="n">
         <v>55.6</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>63.3</v>
+        <v>37.8</v>
       </c>
       <c r="V4" t="n">
-        <v>50</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
+        <v>14.4</v>
+      </c>
+      <c r="W4" t="n">
+        <v>48</v>
+      </c>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1599,12 +1583,12 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1614,117 +1598,117 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.1951</t>
+          <t>0.2549</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.3923</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.1478</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>25.43</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1758,16 +1742,56 @@
         </is>
       </c>
       <c r="BP4" t="inlineStr"/>
-      <c r="BQ4" t="inlineStr"/>
-      <c r="BR4" t="inlineStr"/>
-      <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="inlineStr"/>
-      <c r="BU4" t="inlineStr"/>
-      <c r="BV4" t="inlineStr"/>
-      <c r="BW4" t="inlineStr"/>
-      <c r="BX4" t="inlineStr"/>
-      <c r="BY4" t="inlineStr"/>
-      <c r="BZ4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>Ballpark Pal top hitter 27.9%; best park/weather on slate</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1775,24 +1799,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -1800,19 +1824,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L5" t="n">
-        <v>54.5</v>
+        <v>55.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1826,26 +1862,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>48.9</v>
+        <v>50.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R5" t="n">
         <v>55.6</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>28.9</v>
+        <v>63.3</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -1853,42 +1889,38 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr"/>
@@ -1905,12 +1937,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1920,12 +1952,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1935,78 +1967,102 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.1639</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+          <t>0.1951</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2082,12 +2138,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2106,7 +2162,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>53.9</v>
+        <v>52.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2120,7 +2176,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -2133,7 +2189,7 @@
         <v>55.6</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -2147,39 +2203,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2324,7 +2376,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2375,12 +2427,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2400,12 +2452,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2424,7 +2476,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2438,11 +2490,11 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>47.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q7" t="n">
         <v>40.1</v>
@@ -2451,13 +2503,13 @@
         <v>55.6</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>13.3</v>
+        <v>25.3</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -2465,39 +2517,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2517,7 +2565,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2527,12 +2575,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -2542,72 +2590,72 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -2642,7 +2690,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2693,12 +2741,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2718,19 +2766,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Dustin May</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>669160</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>50.9</v>
+        <v>51.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2744,26 +2804,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.6</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
-        <v>41.2</v>
+        <v>46.2</v>
       </c>
       <c r="R8" t="n">
         <v>55.6</v>
       </c>
       <c r="S8" t="n">
-        <v>71.7</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>54.9</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -2771,42 +2831,38 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr"/>
@@ -2823,27 +2879,27 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -2853,78 +2909,102 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>32.39</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.2134</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+          <t>0.1617</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>44.36</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>90.18</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>0.4132</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>0.1595</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>25.43</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -2975,24 +3055,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -3000,19 +3080,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L9" t="n">
-        <v>50.7</v>
+        <v>50.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3026,26 +3118,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>41</v>
+        <v>39.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R9" t="n">
         <v>55.6</v>
       </c>
       <c r="S9" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>20.9</v>
+        <v>37.8</v>
       </c>
       <c r="V9" t="n">
         <v>50</v>
@@ -3053,42 +3145,38 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr"/>
@@ -3105,27 +3193,27 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -3135,78 +3223,102 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.1617</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+          <t>0.1446</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3257,12 +3369,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3282,12 +3394,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3306,7 +3418,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>50.3</v>
+        <v>48.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3320,11 +3432,11 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>39.5</v>
+        <v>47.1</v>
       </c>
       <c r="Q10" t="n">
         <v>40.1</v>
@@ -3333,13 +3445,13 @@
         <v>55.6</v>
       </c>
       <c r="S10" t="n">
-        <v>90.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T10" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>37.8</v>
+        <v>13.3</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -3347,39 +3459,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3399,7 +3507,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -3409,87 +3517,87 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -3524,7 +3632,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3575,24 +3683,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -3600,22 +3708,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -3624,7 +3732,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>49.1</v>
+        <v>47.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3638,26 +3746,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>38.2</v>
+        <v>43.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>40.1</v>
+        <v>46.2</v>
       </c>
       <c r="R11" t="n">
         <v>55.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>25.3</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -3665,39 +3773,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3717,27 +3821,27 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -3747,102 +3851,102 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>75.91</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>58.98</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.3923</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.1478</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>25.43</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -3918,7 +4022,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3926,11 +4030,23 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Dustin May</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>669160</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>40.6</v>
+        <v>44</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3944,23 +4060,23 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
         <v>7.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>46.2</v>
       </c>
       <c r="R12" t="n">
         <v>55.6</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
         <v>19.5</v>
@@ -3971,42 +4087,38 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -4043,7 +4155,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -4116,15 +4228,39 @@
           <t>0.1347</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>44.36</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>90.18</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>0.4132</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>0.1595</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>25.43</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4200,19 +4336,31 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Dustin May</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>669160</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L13" t="n">
-        <v>39.8</v>
+        <v>43.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4226,23 +4374,23 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
         <v>10.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.2</v>
+        <v>46.2</v>
       </c>
       <c r="R13" t="n">
         <v>55.6</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
         <v>70.59999999999999</v>
@@ -4253,42 +4401,38 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr"/>
@@ -4325,7 +4469,7 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -4398,15 +4542,39 @@
           <t>0.151</t>
         </is>
       </c>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>44.36</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>90.18</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>0.4132</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>0.1595</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>25.43</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4457,24 +4625,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -4482,7 +4650,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4492,12 +4660,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4506,7 +4674,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>37.3</v>
+        <v>40.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4520,26 +4688,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>16.6</v>
+        <v>15.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>38.7</v>
+        <v>46.2</v>
       </c>
       <c r="R14" t="n">
         <v>55.6</v>
       </c>
       <c r="S14" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>5.1</v>
+        <v>19.5</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -4547,42 +4715,38 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr"/>
@@ -4599,12 +4763,12 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -4614,12 +4778,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -4629,102 +4793,102 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.3923</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.1478</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>25.43</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -4775,24 +4939,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -4800,19 +4964,31 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>37</v>
+        <v>39.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4826,26 +5002,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>15.4</v>
+        <v>5.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R15" t="n">
         <v>55.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T15" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>19.5</v>
+        <v>17.3</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -4853,42 +5029,38 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr"/>
@@ -4905,12 +5077,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -4920,12 +5092,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -4935,78 +5107,102 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>0.0974</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5082,19 +5278,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Dustin May</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>669160</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>36.9</v>
+        <v>38.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5108,23 +5316,23 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
         <v>0.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.2</v>
+        <v>46.2</v>
       </c>
       <c r="R16" t="n">
         <v>55.6</v>
       </c>
       <c r="S16" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T16" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
         <v>15.3</v>
@@ -5135,42 +5343,38 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
@@ -5207,7 +5411,7 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -5280,15 +5484,39 @@
           <t>0.05</t>
         </is>
       </c>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>44.36</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>90.18</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>0.4132</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>0.1595</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>25.43</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5364,7 +5592,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5388,7 +5616,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>36.4</v>
+        <v>37</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5402,7 +5630,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -5415,7 +5643,7 @@
         <v>55.6</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>50</v>
@@ -5429,39 +5657,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -5606,7 +5830,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5682,7 +5906,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5706,7 +5930,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>36.2</v>
+        <v>36.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5720,7 +5944,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -5733,7 +5957,7 @@
         <v>55.6</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
         <v>80</v>
@@ -5747,39 +5971,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5924,7 +6144,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6000,7 +6220,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6008,11 +6228,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Dustin May</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>669160</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L19" t="n">
-        <v>34.2</v>
+        <v>35.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6026,20 +6258,20 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
         <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>40.2</v>
+        <v>44.4</v>
       </c>
       <c r="R19" t="n">
         <v>55.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -6053,42 +6285,38 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr"/>
@@ -6125,7 +6353,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -6198,15 +6426,39 @@
           <t>0.0829</t>
         </is>
       </c>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>44.36</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>90.18</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>0.4132</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>0.1595</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>25.43</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -6688,12 +6940,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6712,7 +6964,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>58.1</v>
+        <v>59.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6726,7 +6978,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6739,7 +6991,7 @@
         <v>55.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -6753,39 +7005,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6930,7 +7178,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -6981,12 +7229,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -6996,7 +7244,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -7006,19 +7254,31 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Dustin May</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>669160</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>56.8</v>
+        <v>57.9</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7032,71 +7292,65 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>61.9</v>
+        <v>48.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.2</v>
+        <v>46.2</v>
       </c>
       <c r="R3" t="n">
         <v>55.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U3" t="n">
-        <v>37.8</v>
+        <v>28.9</v>
       </c>
       <c r="V3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W3" t="n">
-        <v>48</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr"/>
@@ -7113,130 +7367,154 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Last 7 games: 4/21, 1 HR</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>10.8</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>48.55</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>91.67</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>101.2282</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.4611</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.196</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.3547</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>70.36</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>13.11</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>33.13</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>30.13</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>44.36</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>90.18</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.4132</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.1595</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>13.37</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>50.21</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>92.61</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>104.9857</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.4996</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.232</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.3586</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>79.13</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>83.64</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>44.89</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>23.28</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>0.2549</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>40 deg</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="BN3" t="inlineStr">
         <is>
           <t>75</t>
@@ -7248,56 +7526,16 @@
         </is>
       </c>
       <c r="BP3" t="inlineStr"/>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>Ballpark Pal top hitter 27.9%; best park/weather on slate</t>
-        </is>
-      </c>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="inlineStr"/>
+      <c r="BX3" t="inlineStr"/>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -7305,22 +7543,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -7330,22 +7568,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -7354,7 +7592,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>54.6</v>
+        <v>57.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7368,66 +7606,64 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>50.1</v>
+        <v>61.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>40.1</v>
+        <v>46.2</v>
       </c>
       <c r="R4" t="n">
         <v>55.6</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>63.3</v>
+        <v>37.8</v>
       </c>
       <c r="V4" t="n">
-        <v>50</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
+        <v>14.4</v>
+      </c>
+      <c r="W4" t="n">
+        <v>48</v>
+      </c>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7447,12 +7683,12 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -7462,117 +7698,117 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.1951</t>
+          <t>0.2549</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.3923</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.1478</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>25.43</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -7606,16 +7842,56 @@
         </is>
       </c>
       <c r="BP4" t="inlineStr"/>
-      <c r="BQ4" t="inlineStr"/>
-      <c r="BR4" t="inlineStr"/>
-      <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="inlineStr"/>
-      <c r="BU4" t="inlineStr"/>
-      <c r="BV4" t="inlineStr"/>
-      <c r="BW4" t="inlineStr"/>
-      <c r="BX4" t="inlineStr"/>
-      <c r="BY4" t="inlineStr"/>
-      <c r="BZ4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>Ballpark Pal top hitter 27.9%; best park/weather on slate</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -7623,24 +7899,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -7648,19 +7924,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L5" t="n">
-        <v>54.5</v>
+        <v>55.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7674,26 +7962,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>48.9</v>
+        <v>50.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R5" t="n">
         <v>55.6</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>28.9</v>
+        <v>63.3</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -7701,42 +7989,38 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr"/>
@@ -7753,12 +8037,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -7768,12 +8052,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -7783,78 +8067,102 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.1639</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+          <t>0.1951</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -7930,12 +8238,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -7954,7 +8262,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>53.9</v>
+        <v>52.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7968,7 +8276,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7981,7 +8289,7 @@
         <v>55.6</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -7995,39 +8303,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8172,7 +8476,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8223,12 +8527,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -8248,12 +8552,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8272,7 +8576,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8286,11 +8590,11 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>47.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q7" t="n">
         <v>40.1</v>
@@ -8299,13 +8603,13 @@
         <v>55.6</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>13.3</v>
+        <v>25.3</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -8313,39 +8617,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8365,7 +8665,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -8375,12 +8675,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -8390,72 +8690,72 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -8490,7 +8790,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8541,12 +8841,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -8566,19 +8866,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Dustin May</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>669160</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>50.9</v>
+        <v>51.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8592,26 +8904,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.6</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
-        <v>41.2</v>
+        <v>46.2</v>
       </c>
       <c r="R8" t="n">
         <v>55.6</v>
       </c>
       <c r="S8" t="n">
-        <v>71.7</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>54.9</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -8619,42 +8931,38 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr"/>
@@ -8671,27 +8979,27 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -8701,78 +9009,102 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>32.39</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.2134</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+          <t>0.1617</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>44.36</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>90.18</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>0.4132</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>0.1595</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>25.43</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -8823,24 +9155,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -8848,19 +9180,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L9" t="n">
-        <v>50.7</v>
+        <v>50.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8874,26 +9218,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>41</v>
+        <v>39.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R9" t="n">
         <v>55.6</v>
       </c>
       <c r="S9" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>20.9</v>
+        <v>37.8</v>
       </c>
       <c r="V9" t="n">
         <v>50</v>
@@ -8901,42 +9245,38 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr"/>
@@ -8953,27 +9293,27 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -8983,78 +9323,102 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.1617</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+          <t>0.1446</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9105,12 +9469,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -9130,12 +9494,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -9154,7 +9518,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>50.3</v>
+        <v>48.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9168,11 +9532,11 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>39.5</v>
+        <v>47.1</v>
       </c>
       <c r="Q10" t="n">
         <v>40.1</v>
@@ -9181,13 +9545,13 @@
         <v>55.6</v>
       </c>
       <c r="S10" t="n">
-        <v>90.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T10" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>37.8</v>
+        <v>13.3</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -9195,39 +9559,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9247,7 +9607,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -9257,87 +9617,87 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9372,7 +9732,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9423,24 +9783,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -9448,22 +9808,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -9472,7 +9832,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>49.1</v>
+        <v>47.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9486,26 +9846,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>38.2</v>
+        <v>43.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>40.1</v>
+        <v>46.2</v>
       </c>
       <c r="R11" t="n">
         <v>55.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>25.3</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -9513,39 +9873,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9565,27 +9921,27 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -9595,102 +9951,102 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>75.91</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>58.98</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.3923</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.1478</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>25.43</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -9766,7 +10122,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -9774,11 +10130,23 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Dustin May</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>669160</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>40.6</v>
+        <v>44</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9792,23 +10160,23 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
         <v>7.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>46.2</v>
       </c>
       <c r="R12" t="n">
         <v>55.6</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
         <v>19.5</v>
@@ -9819,42 +10187,38 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -9891,7 +10255,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -9964,15 +10328,39 @@
           <t>0.1347</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>44.36</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>90.18</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>0.4132</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>0.1595</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>25.43</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10048,19 +10436,31 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Dustin May</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>669160</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L13" t="n">
-        <v>39.8</v>
+        <v>43.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10074,23 +10474,23 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
         <v>10.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.2</v>
+        <v>46.2</v>
       </c>
       <c r="R13" t="n">
         <v>55.6</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
         <v>70.59999999999999</v>
@@ -10101,42 +10501,38 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr"/>
@@ -10173,7 +10569,7 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -10246,15 +10642,39 @@
           <t>0.151</t>
         </is>
       </c>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>44.36</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>90.18</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>0.4132</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>0.1595</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>25.43</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10305,24 +10725,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -10330,7 +10750,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10340,12 +10760,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -10354,7 +10774,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>37.3</v>
+        <v>40.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10368,26 +10788,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>16.6</v>
+        <v>15.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>38.7</v>
+        <v>46.2</v>
       </c>
       <c r="R14" t="n">
         <v>55.6</v>
       </c>
       <c r="S14" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>5.1</v>
+        <v>19.5</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -10395,42 +10815,38 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr"/>
@@ -10447,12 +10863,12 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -10462,12 +10878,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -10477,102 +10893,102 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.3923</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.1478</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>25.43</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -10623,24 +11039,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -10648,19 +11064,31 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>37</v>
+        <v>39.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -10674,26 +11102,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>15.4</v>
+        <v>5.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R15" t="n">
         <v>55.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T15" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>19.5</v>
+        <v>17.3</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -10701,42 +11129,38 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr"/>
@@ -10753,12 +11177,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -10768,12 +11192,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -10783,78 +11207,102 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>0.0974</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -10930,19 +11378,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Dustin May</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>669160</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>36.9</v>
+        <v>38.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10956,23 +11416,23 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
         <v>0.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.2</v>
+        <v>46.2</v>
       </c>
       <c r="R16" t="n">
         <v>55.6</v>
       </c>
       <c r="S16" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T16" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
         <v>15.3</v>
@@ -10983,42 +11443,38 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
@@ -11055,7 +11511,7 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -11128,15 +11584,39 @@
           <t>0.05</t>
         </is>
       </c>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>44.36</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>90.18</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>0.4132</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>0.1595</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>25.43</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11212,7 +11692,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -11236,7 +11716,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>36.4</v>
+        <v>37</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11250,7 +11730,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -11263,7 +11743,7 @@
         <v>55.6</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>50</v>
@@ -11277,39 +11757,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -11454,7 +11930,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -11530,7 +12006,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -11554,7 +12030,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>36.2</v>
+        <v>36.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -11568,7 +12044,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -11581,7 +12057,7 @@
         <v>55.6</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
         <v>80</v>
@@ -11595,39 +12071,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11772,7 +12244,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -11848,7 +12320,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -11856,11 +12328,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Dustin May</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>669160</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L19" t="n">
-        <v>34.2</v>
+        <v>35.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -11874,20 +12358,20 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
         <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>40.2</v>
+        <v>44.4</v>
       </c>
       <c r="R19" t="n">
         <v>55.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -11901,42 +12385,38 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr"/>
@@ -11973,7 +12453,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -12046,15 +12526,39 @@
           <t>0.0829</t>
         </is>
       </c>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>44.36</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>90.18</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>0.4132</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>0.1595</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>25.43</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>40 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
